--- a/Ref docs/Resource/Add Details/Resource Details - Real Data.xlsx
+++ b/Ref docs/Resource/Add Details/Resource Details - Real Data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/anjana_sharma_rockwellautomation_com/Documents/Anjana Sharma - All Important Documents/1. My work/RA Work/AM-APP/Ref docs/Resource/Add Details/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Anjana\AM-APP\Ref docs\Resource\Add Details\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{B2E8D8F5-9C64-446D-9463-DBC50913925C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3ECFC5D1-8409-4FA5-B35E-384AD8E83828}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A47A9B-12CA-40F1-901E-414634397F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2382" uniqueCount="1089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2385" uniqueCount="1094">
   <si>
     <t>S.NO</t>
   </si>
@@ -3020,9 +3020,6 @@
     <t>2019-03-26</t>
   </si>
   <si>
-    <t>8.17 years</t>
-  </si>
-  <si>
     <t>Agile Methodology, Application Testing, Automated Test Scripts, Automation Frameworks, Data Testing, Defect Tracking Tools, Manual Testing, Prioritization, Project Management, RA IT| Amazon Web Services, RA IT| Apache Spark, RA IT| ElasticSearch, RA IT| GitLab, RA IT| Jenkins, RA IT| Jira, RA IT| Microsoft - Desktop, RA IT| MongoDB, RA IT| MS SQL, RA IT| MySQL, RA IT| PostgreSQL, RA IT| PYTHON, RA IT| SQL, Selenium, Software Testing, Software Testing Process, Test Analysis, Test Automation, Test Case Design, Test Development, Test Execution, Test Procedure Development</t>
   </si>
   <si>
@@ -3303,6 +3300,24 @@
   </si>
   <si>
     <t>TBD</t>
+  </si>
+  <si>
+    <t>7.6 years</t>
+  </si>
+  <si>
+    <t>7.4 years</t>
+  </si>
+  <si>
+    <t>9.4 years</t>
+  </si>
+  <si>
+    <t>3.3 years</t>
+  </si>
+  <si>
+    <t>9.6 years</t>
+  </si>
+  <si>
+    <t>0.5 years</t>
   </si>
 </sst>
 </file>
@@ -3878,7 +3893,7 @@
         <v>17</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K2" s="6"/>
     </row>
@@ -3911,7 +3926,7 @@
         <v>22</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K3" s="6"/>
     </row>
@@ -3938,7 +3953,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K4" s="6"/>
     </row>
@@ -3967,7 +3982,7 @@
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K5" s="6" t="s">
         <v>29</v>
@@ -3999,10 +4014,10 @@
         <v>33</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>34</v>
+        <v>311</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K6" s="6"/>
     </row>
@@ -4035,7 +4050,7 @@
         <v>699</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K7" s="6" t="s">
         <v>40</v>
@@ -4070,7 +4085,7 @@
         <v>44</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K8" s="6"/>
     </row>
@@ -4103,7 +4118,7 @@
         <v>50</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K9" s="6" t="s">
         <v>51</v>
@@ -4138,7 +4153,7 @@
         <v>56</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>57</v>
@@ -4173,7 +4188,7 @@
         <v>62</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>63</v>
@@ -4208,7 +4223,7 @@
         <v>66</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K12" s="6" t="s">
         <v>67</v>
@@ -4243,7 +4258,7 @@
         <v>73</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>74</v>
@@ -4278,7 +4293,7 @@
         <v>78</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K14" s="6"/>
     </row>
@@ -4311,7 +4326,7 @@
         <v>82</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>83</v>
@@ -4343,10 +4358,10 @@
         <v>87</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>88</v>
+        <v>462</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>89</v>
@@ -4381,7 +4396,7 @@
         <v>93</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K17" s="6" t="s">
         <v>94</v>
@@ -4416,7 +4431,7 @@
         <v>82</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K18" s="6"/>
     </row>
@@ -4449,7 +4464,7 @@
         <v>100</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K19" s="6"/>
     </row>
@@ -4482,7 +4497,7 @@
         <v>105</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>106</v>
@@ -4513,7 +4528,7 @@
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>110</v>
@@ -4548,7 +4563,7 @@
         <v>44</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K22" s="6"/>
     </row>
@@ -4581,7 +4596,7 @@
         <v>116</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>117</v>
@@ -4616,7 +4631,7 @@
         <v>121</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K24" s="6"/>
     </row>
@@ -4649,7 +4664,7 @@
         <v>128</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K25" s="6" t="s">
         <v>129</v>
@@ -4678,7 +4693,7 @@
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K26" s="6"/>
     </row>
@@ -4711,7 +4726,7 @@
         <v>137</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>138</v>
@@ -4746,7 +4761,7 @@
         <v>142</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>143</v>
@@ -4781,7 +4796,7 @@
         <v>148</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>149</v>
@@ -4816,7 +4831,7 @@
         <v>154</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>155</v>
@@ -4851,7 +4866,7 @@
         <v>105</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>159</v>
@@ -4882,7 +4897,7 @@
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>163</v>
@@ -4917,7 +4932,7 @@
         <v>82</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>166</v>
@@ -4952,7 +4967,7 @@
         <v>116</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>169</v>
@@ -4987,7 +5002,7 @@
         <v>173</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K35" s="6"/>
     </row>
@@ -5020,7 +5035,7 @@
         <v>177</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>178</v>
@@ -5055,7 +5070,7 @@
         <v>182</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K37" s="6"/>
     </row>
@@ -5088,7 +5103,7 @@
         <v>186</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>187</v>
@@ -5123,7 +5138,7 @@
         <v>182</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K39" s="6"/>
     </row>
@@ -5156,7 +5171,7 @@
         <v>194</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>195</v>
@@ -5191,7 +5206,7 @@
         <v>200</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>201</v>
@@ -5226,7 +5241,7 @@
         <v>206</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K42" s="6"/>
     </row>
@@ -5253,7 +5268,7 @@
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>209</v>
@@ -5288,7 +5303,7 @@
         <v>82</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>212</v>
@@ -5323,7 +5338,7 @@
         <v>216</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>217</v>
@@ -5358,7 +5373,7 @@
         <v>220</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>221</v>
@@ -5393,7 +5408,7 @@
         <v>17</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K47" s="6"/>
     </row>
@@ -5426,7 +5441,7 @@
         <v>116</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>226</v>
@@ -5461,7 +5476,7 @@
         <v>231</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>232</v>
@@ -5496,7 +5511,7 @@
         <v>105</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>236</v>
@@ -5527,7 +5542,7 @@
       </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K51" s="6"/>
     </row>
@@ -5560,7 +5575,7 @@
         <v>105</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K52" s="6" t="s">
         <v>242</v>
@@ -5595,7 +5610,7 @@
         <v>247</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>248</v>
@@ -5630,7 +5645,7 @@
         <v>252</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K54" s="6"/>
     </row>
@@ -5663,7 +5678,7 @@
         <v>100</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K55" s="6"/>
     </row>
@@ -5696,7 +5711,7 @@
         <v>260</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>261</v>
@@ -5731,7 +5746,7 @@
         <v>39</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>264</v>
@@ -5766,7 +5781,7 @@
         <v>268</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>269</v>
@@ -5801,7 +5816,7 @@
         <v>82</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K59" s="6"/>
     </row>
@@ -5834,7 +5849,7 @@
         <v>275</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>276</v>
@@ -5865,7 +5880,7 @@
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>279</v>
@@ -5894,7 +5909,7 @@
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K62" s="6"/>
     </row>
@@ -5927,7 +5942,7 @@
         <v>285</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K63" s="6" t="s">
         <v>286</v>
@@ -5958,7 +5973,7 @@
       </c>
       <c r="I64" s="1"/>
       <c r="J64" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K64" s="6"/>
     </row>
@@ -5987,7 +6002,7 @@
       </c>
       <c r="I65" s="1"/>
       <c r="J65" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K65" s="6" t="s">
         <v>291</v>
@@ -6022,7 +6037,7 @@
         <v>295</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>296</v>
@@ -6053,7 +6068,7 @@
       </c>
       <c r="I67" s="1"/>
       <c r="J67" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>299</v>
@@ -6088,7 +6103,7 @@
         <v>252</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>302</v>
@@ -6119,7 +6134,7 @@
       </c>
       <c r="I69" s="1"/>
       <c r="J69" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K69" s="6" t="s">
         <v>305</v>
@@ -6154,7 +6169,7 @@
         <v>311</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>312</v>
@@ -6189,7 +6204,7 @@
         <v>316</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>317</v>
@@ -6224,7 +6239,7 @@
         <v>17</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K72" s="6"/>
     </row>
@@ -6257,7 +6272,7 @@
         <v>82</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K73" s="6"/>
     </row>
@@ -6290,7 +6305,7 @@
         <v>327</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>328</v>
@@ -6325,7 +6340,7 @@
         <v>332</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>333</v>
@@ -6360,7 +6375,7 @@
         <v>337</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>338</v>
@@ -6395,7 +6410,7 @@
         <v>88</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K77" s="6" t="s">
         <v>342</v>
@@ -6426,7 +6441,7 @@
       </c>
       <c r="I78" s="1"/>
       <c r="J78" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>345</v>
@@ -6461,7 +6476,7 @@
         <v>349</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K79" s="6" t="s">
         <v>350</v>
@@ -6496,7 +6511,7 @@
         <v>116</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>353</v>
@@ -6531,7 +6546,7 @@
         <v>82</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>356</v>
@@ -6566,7 +6581,7 @@
         <v>361</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K82" s="6"/>
     </row>
@@ -6599,7 +6614,7 @@
         <v>365</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>366</v>
@@ -6634,7 +6649,7 @@
         <v>369</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K84" s="6" t="s">
         <v>370</v>
@@ -6665,7 +6680,7 @@
       </c>
       <c r="I85" s="1"/>
       <c r="J85" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K85" s="6" t="s">
         <v>373</v>
@@ -6700,7 +6715,7 @@
         <v>82</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>376</v>
@@ -6731,7 +6746,7 @@
       </c>
       <c r="I87" s="1"/>
       <c r="J87" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K87" s="6" t="s">
         <v>379</v>
@@ -6766,7 +6781,7 @@
         <v>220</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K88" s="6" t="s">
         <v>383</v>
@@ -6801,7 +6816,7 @@
         <v>260</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K89" s="6" t="s">
         <v>388</v>
@@ -6836,7 +6851,7 @@
         <v>66</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K90" s="6" t="s">
         <v>391</v>
@@ -6871,7 +6886,7 @@
         <v>396</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K91" s="6"/>
     </row>
@@ -6904,7 +6919,7 @@
         <v>82</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K92" s="6"/>
     </row>
@@ -6937,7 +6952,7 @@
         <v>403</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K93" s="6" t="s">
         <v>404</v>
@@ -6972,7 +6987,7 @@
         <v>82</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K94" s="6" t="s">
         <v>407</v>
@@ -7007,7 +7022,7 @@
         <v>116</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K95" s="6"/>
     </row>
@@ -7040,7 +7055,7 @@
         <v>66</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K96" s="6" t="s">
         <v>412</v>
@@ -7075,7 +7090,7 @@
         <v>62</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K97" s="6" t="s">
         <v>415</v>
@@ -7110,7 +7125,7 @@
         <v>419</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K98" s="6" t="s">
         <v>420</v>
@@ -7139,7 +7154,7 @@
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
       <c r="J99" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K99" s="6" t="s">
         <v>423</v>
@@ -7174,7 +7189,7 @@
         <v>247</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K100" s="6" t="s">
         <v>427</v>
@@ -7209,7 +7224,7 @@
         <v>419</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K101" s="6"/>
     </row>
@@ -7242,7 +7257,7 @@
         <v>434</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K102" s="6" t="s">
         <v>435</v>
@@ -7277,7 +7292,7 @@
         <v>439</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K103" s="6" t="s">
         <v>440</v>
@@ -7312,7 +7327,7 @@
         <v>295</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K104" s="6" t="s">
         <v>444</v>
@@ -7347,7 +7362,7 @@
         <v>82</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K105" s="6" t="s">
         <v>447</v>
@@ -7382,7 +7397,7 @@
         <v>177</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K106" s="6" t="s">
         <v>452</v>
@@ -7417,7 +7432,7 @@
         <v>105</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K107" s="6"/>
     </row>
@@ -7450,7 +7465,7 @@
         <v>182</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K108" s="6"/>
     </row>
@@ -7483,7 +7498,7 @@
         <v>462</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K109" s="6"/>
     </row>
@@ -7516,7 +7531,7 @@
         <v>231</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K110" s="6"/>
     </row>
@@ -7545,7 +7560,7 @@
       <c r="H111" s="1"/>
       <c r="I111" s="1"/>
       <c r="J111" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K111" s="6" t="s">
         <v>468</v>
@@ -7576,7 +7591,7 @@
       </c>
       <c r="I112" s="1"/>
       <c r="J112" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K112" s="6"/>
     </row>
@@ -7609,7 +7624,7 @@
         <v>275</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K113" s="6" t="s">
         <v>473</v>
@@ -7644,7 +7659,7 @@
         <v>194</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K114" s="6"/>
     </row>
@@ -7677,7 +7692,7 @@
         <v>206</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K115" s="6" t="s">
         <v>481</v>
@@ -7712,7 +7727,7 @@
         <v>337</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K116" s="6" t="s">
         <v>486</v>
@@ -7743,7 +7758,7 @@
       </c>
       <c r="I117" s="1"/>
       <c r="J117" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K117" s="6" t="s">
         <v>489</v>
@@ -7778,7 +7793,7 @@
         <v>493</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K118" s="6" t="s">
         <v>494</v>
@@ -7809,7 +7824,7 @@
       </c>
       <c r="I119" s="1"/>
       <c r="J119" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K119" s="6" t="s">
         <v>497</v>
@@ -7844,7 +7859,7 @@
         <v>173</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K120" s="6" t="s">
         <v>501</v>
@@ -7879,7 +7894,7 @@
         <v>439</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K121" s="6" t="s">
         <v>505</v>
@@ -7914,7 +7929,7 @@
         <v>439</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K122" s="6" t="s">
         <v>509</v>
@@ -7949,7 +7964,7 @@
         <v>82</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K123" s="6" t="s">
         <v>512</v>
@@ -7984,7 +7999,7 @@
         <v>62</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K124" s="6"/>
     </row>
@@ -8017,7 +8032,7 @@
         <v>78</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K125" s="6" t="s">
         <v>520</v>
@@ -8052,7 +8067,7 @@
         <v>88</v>
       </c>
       <c r="J126" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K126" s="6" t="s">
         <v>524</v>
@@ -8087,7 +8102,7 @@
         <v>528</v>
       </c>
       <c r="J127" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K127" s="6"/>
     </row>
@@ -8120,7 +8135,7 @@
         <v>532</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K128" s="6" t="s">
         <v>533</v>
@@ -8155,7 +8170,7 @@
         <v>173</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K129" s="6" t="s">
         <v>536</v>
@@ -8190,7 +8205,7 @@
         <v>39</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K130" s="6" t="s">
         <v>539</v>
@@ -8219,9 +8234,11 @@
         <v>542</v>
       </c>
       <c r="H131" s="1"/>
-      <c r="I131" s="1"/>
+      <c r="I131" s="1" t="s">
+        <v>1090</v>
+      </c>
       <c r="J131" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K131" s="6" t="s">
         <v>543</v>
@@ -8256,7 +8273,7 @@
         <v>105</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K132" s="6" t="s">
         <v>547</v>
@@ -8291,7 +8308,7 @@
         <v>17</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K133" s="6" t="s">
         <v>550</v>
@@ -8326,7 +8343,7 @@
         <v>555</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K134" s="6"/>
     </row>
@@ -8359,7 +8376,7 @@
         <v>105</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K135" s="6" t="s">
         <v>558</v>
@@ -8394,7 +8411,7 @@
         <v>252</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K136" s="6"/>
     </row>
@@ -8427,7 +8444,7 @@
         <v>88</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K137" s="6"/>
     </row>
@@ -8460,7 +8477,7 @@
         <v>252</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K138" s="6"/>
     </row>
@@ -8493,7 +8510,7 @@
         <v>17</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K139" s="6"/>
     </row>
@@ -8526,7 +8543,7 @@
         <v>93</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K140" s="6" t="s">
         <v>572</v>
@@ -8561,7 +8578,7 @@
         <v>177</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K141" s="6" t="s">
         <v>575</v>
@@ -8596,7 +8613,7 @@
         <v>337</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K142" s="6" t="s">
         <v>580</v>
@@ -8628,10 +8645,10 @@
         <v>584</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>39</v>
+        <v>699</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K143" s="6" t="s">
         <v>585</v>
@@ -8666,7 +8683,7 @@
         <v>82</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K144" s="6" t="s">
         <v>588</v>
@@ -8701,7 +8718,7 @@
         <v>592</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K145" s="6" t="s">
         <v>593</v>
@@ -8736,7 +8753,7 @@
         <v>17</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K146" s="6"/>
     </row>
@@ -8765,7 +8782,7 @@
       <c r="H147" s="1"/>
       <c r="I147" s="1"/>
       <c r="J147" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K147" s="6" t="s">
         <v>598</v>
@@ -8800,7 +8817,7 @@
         <v>62</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K148" s="6" t="s">
         <v>602</v>
@@ -8835,7 +8852,7 @@
         <v>606</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K149" s="6" t="s">
         <v>607</v>
@@ -8870,7 +8887,7 @@
         <v>419</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K150" s="6" t="s">
         <v>611</v>
@@ -8905,7 +8922,7 @@
         <v>88</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K151" s="6" t="s">
         <v>614</v>
@@ -8934,7 +8951,7 @@
       <c r="H152" s="1"/>
       <c r="I152" s="1"/>
       <c r="J152" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K152" s="6" t="s">
         <v>617</v>
@@ -8969,7 +8986,7 @@
         <v>621</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K153" s="6" t="s">
         <v>622</v>
@@ -9004,7 +9021,7 @@
         <v>439</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K154" s="6" t="s">
         <v>625</v>
@@ -9039,7 +9056,7 @@
         <v>105</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K155" s="6"/>
     </row>
@@ -9072,7 +9089,7 @@
         <v>632</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K156" s="6" t="s">
         <v>633</v>
@@ -9107,7 +9124,7 @@
         <v>637</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K157" s="6"/>
     </row>
@@ -9140,7 +9157,7 @@
         <v>642</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K158" s="6" t="s">
         <v>643</v>
@@ -9175,7 +9192,7 @@
         <v>647</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K159" s="6" t="s">
         <v>648</v>
@@ -9206,7 +9223,7 @@
       <c r="H160" s="1"/>
       <c r="I160" s="1"/>
       <c r="J160" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K160" s="6"/>
     </row>
@@ -9239,7 +9256,7 @@
         <v>439</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K161" s="6" t="s">
         <v>654</v>
@@ -9274,7 +9291,7 @@
         <v>206</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K162" s="6"/>
     </row>
@@ -9303,7 +9320,7 @@
       </c>
       <c r="I163" s="1"/>
       <c r="J163" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K163" s="6"/>
     </row>
@@ -9330,11 +9347,11 @@
         <v>662</v>
       </c>
       <c r="H164" s="1"/>
-      <c r="I164" s="1">
-        <v>7.4</v>
+      <c r="I164" s="1" t="s">
+        <v>1089</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K164" s="6" t="s">
         <v>663</v>
@@ -9369,7 +9386,7 @@
         <v>17</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K165" s="6"/>
     </row>
@@ -9402,7 +9419,7 @@
         <v>56</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K166" s="6" t="s">
         <v>669</v>
@@ -9437,7 +9454,7 @@
         <v>606</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K167" s="6"/>
     </row>
@@ -9470,7 +9487,7 @@
         <v>275</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K168" s="6" t="s">
         <v>676</v>
@@ -9505,7 +9522,7 @@
         <v>680</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K169" s="6" t="s">
         <v>681</v>
@@ -9540,7 +9557,7 @@
         <v>82</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K170" s="6" t="s">
         <v>684</v>
@@ -9575,7 +9592,7 @@
         <v>82</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K171" s="6"/>
     </row>
@@ -9608,7 +9625,7 @@
         <v>369</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K172" s="6" t="s">
         <v>690</v>
@@ -9643,7 +9660,7 @@
         <v>137</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K173" s="6"/>
     </row>
@@ -9676,7 +9693,7 @@
         <v>78</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K174" s="6"/>
     </row>
@@ -9709,7 +9726,7 @@
         <v>699</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K175" s="6"/>
     </row>
@@ -9736,7 +9753,7 @@
       <c r="H176" s="1"/>
       <c r="I176" s="1"/>
       <c r="J176" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K176" s="6" t="s">
         <v>702</v>
@@ -9771,7 +9788,7 @@
         <v>82</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K177" s="6" t="s">
         <v>705</v>
@@ -9806,7 +9823,7 @@
         <v>186</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K178" s="6" t="s">
         <v>709</v>
@@ -9841,7 +9858,7 @@
         <v>713</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K179" s="6" t="s">
         <v>714</v>
@@ -9876,7 +9893,7 @@
         <v>177</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K180" s="6" t="s">
         <v>717</v>
@@ -9911,7 +9928,7 @@
         <v>532</v>
       </c>
       <c r="J181" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K181" s="6"/>
     </row>
@@ -9940,7 +9957,7 @@
       </c>
       <c r="I182" s="1"/>
       <c r="J182" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K182" s="6" t="s">
         <v>723</v>
@@ -9975,7 +9992,7 @@
         <v>727</v>
       </c>
       <c r="J183" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K183" s="6" t="s">
         <v>728</v>
@@ -10010,7 +10027,7 @@
         <v>732</v>
       </c>
       <c r="J184" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K184" s="6" t="s">
         <v>733</v>
@@ -10045,7 +10062,7 @@
         <v>82</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K185" s="6" t="s">
         <v>737</v>
@@ -10076,7 +10093,7 @@
       </c>
       <c r="I186" s="1"/>
       <c r="J186" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K186" s="6" t="s">
         <v>741</v>
@@ -10111,7 +10128,7 @@
         <v>206</v>
       </c>
       <c r="J187" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K187" s="6" t="s">
         <v>744</v>
@@ -10146,7 +10163,7 @@
         <v>749</v>
       </c>
       <c r="J188" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K188" s="6" t="s">
         <v>750</v>
@@ -10181,7 +10198,7 @@
         <v>82</v>
       </c>
       <c r="J189" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K189" s="6" t="s">
         <v>753</v>
@@ -10216,7 +10233,7 @@
         <v>82</v>
       </c>
       <c r="J190" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K190" s="6" t="s">
         <v>756</v>
@@ -10251,7 +10268,7 @@
         <v>17</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K191" s="6" t="s">
         <v>760</v>
@@ -10286,7 +10303,7 @@
         <v>17</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K192" s="6"/>
     </row>
@@ -10313,7 +10330,7 @@
       <c r="H193" s="1"/>
       <c r="I193" s="1"/>
       <c r="J193" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K193" s="6"/>
     </row>
@@ -10346,7 +10363,7 @@
         <v>768</v>
       </c>
       <c r="J194" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K194" s="6" t="s">
         <v>769</v>
@@ -10377,7 +10394,7 @@
       </c>
       <c r="I195" s="1"/>
       <c r="J195" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K195" s="6" t="s">
         <v>772</v>
@@ -10412,7 +10429,7 @@
         <v>439</v>
       </c>
       <c r="J196" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K196" s="6" t="s">
         <v>775</v>
@@ -10447,7 +10464,7 @@
         <v>177</v>
       </c>
       <c r="J197" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K197" s="6" t="s">
         <v>778</v>
@@ -10482,7 +10499,7 @@
         <v>82</v>
       </c>
       <c r="J198" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K198" s="6" t="s">
         <v>781</v>
@@ -10517,7 +10534,7 @@
         <v>592</v>
       </c>
       <c r="J199" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K199" s="6" t="s">
         <v>785</v>
@@ -10549,10 +10566,10 @@
         <v>788</v>
       </c>
       <c r="I200" s="1" t="s">
-        <v>732</v>
+        <v>1092</v>
       </c>
       <c r="J200" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K200" s="6" t="s">
         <v>789</v>
@@ -10587,7 +10604,7 @@
         <v>680</v>
       </c>
       <c r="J201" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K201" s="6" t="s">
         <v>792</v>
@@ -10622,7 +10639,7 @@
         <v>797</v>
       </c>
       <c r="J202" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K202" s="6" t="s">
         <v>798</v>
@@ -10657,7 +10674,7 @@
         <v>82</v>
       </c>
       <c r="J203" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K203" s="6" t="s">
         <v>801</v>
@@ -10692,7 +10709,7 @@
         <v>34</v>
       </c>
       <c r="J204" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K204" s="6" t="s">
         <v>806</v>
@@ -10727,7 +10744,7 @@
         <v>811</v>
       </c>
       <c r="J205" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K205" s="6" t="s">
         <v>812</v>
@@ -10762,7 +10779,7 @@
         <v>17</v>
       </c>
       <c r="J206" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K206" s="6"/>
     </row>
@@ -10791,7 +10808,7 @@
       </c>
       <c r="I207" s="1"/>
       <c r="J207" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K207" s="6" t="s">
         <v>817</v>
@@ -10826,7 +10843,7 @@
         <v>82</v>
       </c>
       <c r="J208" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K208" s="6" t="s">
         <v>820</v>
@@ -10861,7 +10878,7 @@
         <v>295</v>
       </c>
       <c r="J209" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K209" s="6" t="s">
         <v>824</v>
@@ -10896,7 +10913,7 @@
         <v>828</v>
       </c>
       <c r="J210" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K210" s="6" t="s">
         <v>829</v>
@@ -10931,7 +10948,7 @@
         <v>82</v>
       </c>
       <c r="J211" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K211" s="6" t="s">
         <v>832</v>
@@ -10962,7 +10979,7 @@
       </c>
       <c r="I212" s="1"/>
       <c r="J212" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K212" s="6" t="s">
         <v>836</v>
@@ -10997,7 +11014,7 @@
         <v>128</v>
       </c>
       <c r="J213" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K213" s="6" t="s">
         <v>840</v>
@@ -11032,7 +11049,7 @@
         <v>844</v>
       </c>
       <c r="J214" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K214" s="6" t="s">
         <v>845</v>
@@ -11067,7 +11084,7 @@
         <v>100</v>
       </c>
       <c r="J215" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K215" s="6" t="s">
         <v>848</v>
@@ -11098,7 +11115,7 @@
       </c>
       <c r="I216" s="1"/>
       <c r="J216" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K216" s="6" t="s">
         <v>851</v>
@@ -11133,7 +11150,7 @@
         <v>82</v>
       </c>
       <c r="J217" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K217" s="6" t="s">
         <v>854</v>
@@ -11168,7 +11185,7 @@
         <v>858</v>
       </c>
       <c r="J218" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K218" s="6" t="s">
         <v>859</v>
@@ -11203,7 +11220,7 @@
         <v>337</v>
       </c>
       <c r="J219" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K219" s="6" t="s">
         <v>863</v>
@@ -11238,7 +11255,7 @@
         <v>606</v>
       </c>
       <c r="J220" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K220" s="6"/>
     </row>
@@ -11271,7 +11288,7 @@
         <v>699</v>
       </c>
       <c r="J221" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K221" s="6" t="s">
         <v>870</v>
@@ -11306,7 +11323,7 @@
         <v>137</v>
       </c>
       <c r="J222" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K222" s="6" t="s">
         <v>874</v>
@@ -11341,7 +11358,7 @@
         <v>878</v>
       </c>
       <c r="J223" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K223" s="6"/>
     </row>
@@ -11374,7 +11391,7 @@
         <v>17</v>
       </c>
       <c r="J224" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K224" s="6"/>
     </row>
@@ -11401,7 +11418,7 @@
       <c r="H225" s="1"/>
       <c r="I225" s="1"/>
       <c r="J225" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K225" s="6"/>
     </row>
@@ -11434,7 +11451,7 @@
         <v>439</v>
       </c>
       <c r="J226" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K226" s="6" t="s">
         <v>886</v>
@@ -11469,7 +11486,7 @@
         <v>17</v>
       </c>
       <c r="J227" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K227" s="6" t="s">
         <v>889</v>
@@ -11504,7 +11521,7 @@
         <v>311</v>
       </c>
       <c r="J228" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K228" s="6" t="s">
         <v>893</v>
@@ -11539,7 +11556,7 @@
         <v>17</v>
       </c>
       <c r="J229" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K229" s="6"/>
     </row>
@@ -11566,7 +11583,7 @@
       <c r="H230" s="1"/>
       <c r="I230" s="1"/>
       <c r="J230" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K230" s="6"/>
     </row>
@@ -11599,7 +11616,7 @@
         <v>62</v>
       </c>
       <c r="J231" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K231" s="6" t="s">
         <v>900</v>
@@ -11634,7 +11651,7 @@
         <v>632</v>
       </c>
       <c r="J232" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K232" s="6" t="s">
         <v>904</v>
@@ -11669,7 +11686,7 @@
         <v>908</v>
       </c>
       <c r="J233" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K233" s="6" t="s">
         <v>909</v>
@@ -11704,7 +11721,7 @@
         <v>82</v>
       </c>
       <c r="J234" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K234" s="6"/>
     </row>
@@ -11737,7 +11754,7 @@
         <v>439</v>
       </c>
       <c r="J235" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K235" s="6"/>
     </row>
@@ -11770,7 +11787,7 @@
         <v>528</v>
       </c>
       <c r="J236" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K236" s="6" t="s">
         <v>916</v>
@@ -11805,7 +11822,7 @@
         <v>920</v>
       </c>
       <c r="J237" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K237" s="6" t="s">
         <v>921</v>
@@ -11840,7 +11857,7 @@
         <v>528</v>
       </c>
       <c r="J238" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K238" s="6" t="s">
         <v>925</v>
@@ -11875,7 +11892,7 @@
         <v>82</v>
       </c>
       <c r="J239" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K239" s="6" t="s">
         <v>928</v>
@@ -11910,7 +11927,7 @@
         <v>931</v>
       </c>
       <c r="J240" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K240" s="6"/>
     </row>
@@ -11943,7 +11960,7 @@
         <v>462</v>
       </c>
       <c r="J241" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K241" s="6" t="s">
         <v>935</v>
@@ -11978,7 +11995,7 @@
         <v>439</v>
       </c>
       <c r="J242" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K242" s="6" t="s">
         <v>938</v>
@@ -12013,7 +12030,7 @@
         <v>105</v>
       </c>
       <c r="J243" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K243" s="6"/>
     </row>
@@ -12046,7 +12063,7 @@
         <v>82</v>
       </c>
       <c r="J244" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K244" s="6" t="s">
         <v>943</v>
@@ -12081,7 +12098,7 @@
         <v>946</v>
       </c>
       <c r="J245" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K245" s="6" t="s">
         <v>947</v>
@@ -12116,7 +12133,7 @@
         <v>952</v>
       </c>
       <c r="J246" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K246" s="6"/>
     </row>
@@ -12149,7 +12166,7 @@
         <v>311</v>
       </c>
       <c r="J247" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K247" s="6" t="s">
         <v>956</v>
@@ -12184,7 +12201,7 @@
         <v>439</v>
       </c>
       <c r="J248" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K248" s="6" t="s">
         <v>959</v>
@@ -12213,9 +12230,11 @@
         <v>749</v>
       </c>
       <c r="H249" s="1"/>
-      <c r="I249" s="1"/>
+      <c r="I249" s="1" t="s">
+        <v>1091</v>
+      </c>
       <c r="J249" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K249" s="6" t="s">
         <v>962</v>
@@ -12250,7 +12269,7 @@
         <v>186</v>
       </c>
       <c r="J250" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K250" s="6" t="s">
         <v>965</v>
@@ -12285,7 +12304,7 @@
         <v>39</v>
       </c>
       <c r="J251" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K251" s="6" t="s">
         <v>970</v>
@@ -12320,7 +12339,7 @@
         <v>34</v>
       </c>
       <c r="J252" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K252" s="6"/>
     </row>
@@ -12353,7 +12372,7 @@
         <v>419</v>
       </c>
       <c r="J253" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K253" s="6" t="s">
         <v>978</v>
@@ -12388,7 +12407,7 @@
         <v>419</v>
       </c>
       <c r="J254" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K254" s="6" t="s">
         <v>981</v>
@@ -12423,7 +12442,7 @@
         <v>82</v>
       </c>
       <c r="J255" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K255" s="6" t="s">
         <v>984</v>
@@ -12458,7 +12477,7 @@
         <v>908</v>
       </c>
       <c r="J256" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K256" s="6"/>
     </row>
@@ -12487,7 +12506,7 @@
       <c r="H257" s="1"/>
       <c r="I257" s="1"/>
       <c r="J257" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K257" s="6" t="s">
         <v>990</v>
@@ -12519,13 +12538,13 @@
         <v>993</v>
       </c>
       <c r="I258" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="J258" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K258" s="6" t="s">
         <v>994</v>
-      </c>
-      <c r="J258" s="1" t="s">
-        <v>1088</v>
-      </c>
-      <c r="K258" s="6" t="s">
-        <v>995</v>
       </c>
     </row>
     <row r="259" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -12536,10 +12555,10 @@
         <v>90721957</v>
       </c>
       <c r="C259" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="D259" s="1" t="s">
         <v>996</v>
-      </c>
-      <c r="D259" s="1" t="s">
-        <v>997</v>
       </c>
       <c r="E259" s="1" t="s">
         <v>13</v>
@@ -12551,16 +12570,16 @@
         <v>15</v>
       </c>
       <c r="H259" s="1" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="I259" s="1" t="s">
         <v>78</v>
       </c>
       <c r="J259" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K259" s="6" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="260" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -12571,10 +12590,10 @@
         <v>90719714</v>
       </c>
       <c r="C260" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="D260" s="1" t="s">
         <v>1000</v>
-      </c>
-      <c r="D260" s="1" t="s">
-        <v>1001</v>
       </c>
       <c r="E260" s="1" t="s">
         <v>13</v>
@@ -12586,13 +12605,13 @@
         <v>229</v>
       </c>
       <c r="H260" s="1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="I260" s="1" t="s">
         <v>1002</v>
       </c>
-      <c r="I260" s="1" t="s">
-        <v>1003</v>
-      </c>
       <c r="J260" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K260" s="6"/>
     </row>
@@ -12604,10 +12623,10 @@
         <v>90727174</v>
       </c>
       <c r="C261" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D261" s="1" t="s">
         <v>1004</v>
-      </c>
-      <c r="D261" s="1" t="s">
-        <v>1005</v>
       </c>
       <c r="E261" s="1" t="s">
         <v>13</v>
@@ -12625,7 +12644,7 @@
         <v>17</v>
       </c>
       <c r="J261" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K261" s="6"/>
     </row>
@@ -12637,10 +12656,10 @@
         <v>90719963</v>
       </c>
       <c r="C262" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D262" s="1" t="s">
         <v>1006</v>
-      </c>
-      <c r="D262" s="1" t="s">
-        <v>1007</v>
       </c>
       <c r="E262" s="1" t="s">
         <v>13</v>
@@ -12658,10 +12677,10 @@
         <v>82</v>
       </c>
       <c r="J262" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K262" s="6" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="263" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -12672,10 +12691,10 @@
         <v>90719653</v>
       </c>
       <c r="C263" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D263" s="1" t="s">
         <v>1009</v>
-      </c>
-      <c r="D263" s="1" t="s">
-        <v>1010</v>
       </c>
       <c r="E263" s="1" t="s">
         <v>13</v>
@@ -12687,16 +12706,16 @@
         <v>15</v>
       </c>
       <c r="H263" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="I263" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="J263" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K263" s="6" t="s">
         <v>1011</v>
-      </c>
-      <c r="I263" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J263" s="1" t="s">
-        <v>1088</v>
-      </c>
-      <c r="K263" s="6" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="264" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -12707,10 +12726,10 @@
         <v>90719381</v>
       </c>
       <c r="C264" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D264" s="1" t="s">
         <v>1013</v>
-      </c>
-      <c r="D264" s="1" t="s">
-        <v>1014</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>13</v>
@@ -12719,16 +12738,16 @@
         <v>20</v>
       </c>
       <c r="G264" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H264" s="1" t="s">
         <v>1015</v>
-      </c>
-      <c r="H264" s="1" t="s">
-        <v>1016</v>
       </c>
       <c r="I264" s="1" t="s">
         <v>396</v>
       </c>
       <c r="J264" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K264" s="6"/>
     </row>
@@ -12740,10 +12759,10 @@
         <v>90719534</v>
       </c>
       <c r="C265" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D265" s="1" t="s">
         <v>1017</v>
-      </c>
-      <c r="D265" s="1" t="s">
-        <v>1018</v>
       </c>
       <c r="E265" s="1" t="s">
         <v>32</v>
@@ -12761,10 +12780,10 @@
         <v>182</v>
       </c>
       <c r="J265" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K265" s="6" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="266" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -12775,10 +12794,10 @@
         <v>90732338</v>
       </c>
       <c r="C266" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D266" s="1" t="s">
         <v>1020</v>
-      </c>
-      <c r="D266" s="1" t="s">
-        <v>1021</v>
       </c>
       <c r="E266" s="1" t="s">
         <v>13</v>
@@ -12792,7 +12811,7 @@
       </c>
       <c r="I266" s="1"/>
       <c r="J266" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K266" s="6"/>
     </row>
@@ -12804,10 +12823,10 @@
         <v>90730605</v>
       </c>
       <c r="C267" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D267" s="1" t="s">
         <v>1022</v>
-      </c>
-      <c r="D267" s="1" t="s">
-        <v>1023</v>
       </c>
       <c r="E267" s="1" t="s">
         <v>13</v>
@@ -12816,19 +12835,19 @@
         <v>27</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>229</v>
+        <v>394</v>
       </c>
       <c r="H267" s="1" t="s">
         <v>748</v>
       </c>
       <c r="I267" s="1" t="s">
-        <v>528</v>
+        <v>1093</v>
       </c>
       <c r="J267" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K267" s="6" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="268" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -12839,10 +12858,10 @@
         <v>90732310</v>
       </c>
       <c r="C268" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D268" s="1" t="s">
         <v>1025</v>
-      </c>
-      <c r="D268" s="1" t="s">
-        <v>1026</v>
       </c>
       <c r="E268" s="1" t="s">
         <v>13</v>
@@ -12856,10 +12875,10 @@
       </c>
       <c r="I268" s="1"/>
       <c r="J268" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K268" s="6" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="269" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -12870,10 +12889,10 @@
         <v>90719006</v>
       </c>
       <c r="C269" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D269" s="1" t="s">
         <v>1028</v>
-      </c>
-      <c r="D269" s="1" t="s">
-        <v>1029</v>
       </c>
       <c r="E269" s="1" t="s">
         <v>32</v>
@@ -12882,19 +12901,19 @@
         <v>125</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="H269" s="1" t="s">
         <v>885</v>
       </c>
       <c r="I269" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="J269" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K269" s="6" t="s">
         <v>1031</v>
-      </c>
-      <c r="J269" s="1" t="s">
-        <v>1088</v>
-      </c>
-      <c r="K269" s="6" t="s">
-        <v>1032</v>
       </c>
     </row>
     <row r="270" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -12905,10 +12924,10 @@
         <v>90719871</v>
       </c>
       <c r="C270" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D270" s="1" t="s">
         <v>1033</v>
-      </c>
-      <c r="D270" s="1" t="s">
-        <v>1034</v>
       </c>
       <c r="E270" s="1" t="s">
         <v>13</v>
@@ -12920,13 +12939,13 @@
         <v>15</v>
       </c>
       <c r="H270" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="I270" s="1" t="s">
         <v>82</v>
       </c>
       <c r="J270" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K270" s="6"/>
     </row>
@@ -12938,10 +12957,10 @@
         <v>90719921</v>
       </c>
       <c r="C271" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D271" s="1" t="s">
         <v>1036</v>
-      </c>
-      <c r="D271" s="1" t="s">
-        <v>1037</v>
       </c>
       <c r="E271" s="1" t="s">
         <v>13</v>
@@ -12959,10 +12978,10 @@
         <v>82</v>
       </c>
       <c r="J271" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K271" s="6" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="272" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -12973,10 +12992,10 @@
         <v>90719805</v>
       </c>
       <c r="C272" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D272" s="1" t="s">
         <v>1039</v>
-      </c>
-      <c r="D272" s="1" t="s">
-        <v>1040</v>
       </c>
       <c r="E272" s="1" t="s">
         <v>13</v>
@@ -12994,7 +13013,7 @@
         <v>528</v>
       </c>
       <c r="J272" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K272" s="6"/>
     </row>
@@ -13006,10 +13025,10 @@
         <v>90718836</v>
       </c>
       <c r="C273" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D273" s="1" t="s">
         <v>1041</v>
-      </c>
-      <c r="D273" s="1" t="s">
-        <v>1042</v>
       </c>
       <c r="E273" s="1" t="s">
         <v>32</v>
@@ -13021,16 +13040,16 @@
         <v>450</v>
       </c>
       <c r="H273" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="I273" s="1" t="s">
         <v>1043</v>
       </c>
-      <c r="I273" s="1" t="s">
+      <c r="J273" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K273" s="6" t="s">
         <v>1044</v>
-      </c>
-      <c r="J273" s="1" t="s">
-        <v>1088</v>
-      </c>
-      <c r="K273" s="6" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="274" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -13041,10 +13060,10 @@
         <v>90727541</v>
       </c>
       <c r="C274" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D274" s="1" t="s">
         <v>1046</v>
-      </c>
-      <c r="D274" s="1" t="s">
-        <v>1047</v>
       </c>
       <c r="E274" s="1" t="s">
         <v>32</v>
@@ -13056,7 +13075,7 @@
       <c r="H274" s="1"/>
       <c r="I274" s="1"/>
       <c r="J274" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K274" s="6"/>
     </row>
@@ -13068,10 +13087,10 @@
         <v>90719316</v>
       </c>
       <c r="C275" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D275" s="1" t="s">
         <v>1048</v>
-      </c>
-      <c r="D275" s="1" t="s">
-        <v>1049</v>
       </c>
       <c r="E275" s="1" t="s">
         <v>13</v>
@@ -13083,16 +13102,16 @@
         <v>15</v>
       </c>
       <c r="H275" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="I275" s="1" t="s">
         <v>1050</v>
       </c>
-      <c r="I275" s="1" t="s">
+      <c r="J275" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K275" s="6" t="s">
         <v>1051</v>
-      </c>
-      <c r="J275" s="1" t="s">
-        <v>1088</v>
-      </c>
-      <c r="K275" s="6" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="276" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -13103,10 +13122,10 @@
         <v>90718940</v>
       </c>
       <c r="C276" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D276" s="1" t="s">
         <v>1053</v>
-      </c>
-      <c r="D276" s="1" t="s">
-        <v>1054</v>
       </c>
       <c r="E276" s="1" t="s">
         <v>124</v>
@@ -13118,16 +13137,16 @@
         <v>476</v>
       </c>
       <c r="H276" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="I276" s="1" t="s">
         <v>1055</v>
       </c>
-      <c r="I276" s="1" t="s">
+      <c r="J276" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K276" s="6" t="s">
         <v>1056</v>
-      </c>
-      <c r="J276" s="1" t="s">
-        <v>1088</v>
-      </c>
-      <c r="K276" s="6" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="277" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -13138,10 +13157,10 @@
         <v>90719584</v>
       </c>
       <c r="C277" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D277" s="1" t="s">
         <v>1058</v>
-      </c>
-      <c r="D277" s="1" t="s">
-        <v>1059</v>
       </c>
       <c r="E277" s="1" t="s">
         <v>13</v>
@@ -13153,16 +13172,16 @@
         <v>15</v>
       </c>
       <c r="H277" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>768</v>
       </c>
       <c r="J277" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K277" s="6" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="278" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -13173,10 +13192,10 @@
         <v>90727329</v>
       </c>
       <c r="C278" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D278" s="1" t="s">
         <v>1062</v>
-      </c>
-      <c r="D278" s="1" t="s">
-        <v>1063</v>
       </c>
       <c r="E278" s="1" t="s">
         <v>13</v>
@@ -13185,12 +13204,12 @@
         <v>14</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="H278" s="1"/>
       <c r="I278" s="1"/>
       <c r="J278" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K278" s="6"/>
     </row>
@@ -13202,10 +13221,10 @@
         <v>90732272</v>
       </c>
       <c r="C279" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D279" s="1" t="s">
         <v>1065</v>
-      </c>
-      <c r="D279" s="1" t="s">
-        <v>1066</v>
       </c>
       <c r="E279" s="1" t="s">
         <v>13</v>
@@ -13219,10 +13238,10 @@
       </c>
       <c r="I279" s="1"/>
       <c r="J279" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K279" s="6" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="280" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -13233,10 +13252,10 @@
         <v>90719569</v>
       </c>
       <c r="C280" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D280" s="1" t="s">
         <v>1068</v>
-      </c>
-      <c r="D280" s="1" t="s">
-        <v>1069</v>
       </c>
       <c r="E280" s="1" t="s">
         <v>13</v>
@@ -13245,19 +13264,19 @@
         <v>109</v>
       </c>
       <c r="G280" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="H280" s="1" t="s">
         <v>1070</v>
       </c>
-      <c r="H280" s="1" t="s">
+      <c r="I280" s="1" t="s">
         <v>1071</v>
       </c>
-      <c r="I280" s="1" t="s">
+      <c r="J280" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K280" s="6" t="s">
         <v>1072</v>
-      </c>
-      <c r="J280" s="1" t="s">
-        <v>1088</v>
-      </c>
-      <c r="K280" s="6" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="281" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -13268,10 +13287,10 @@
         <v>90719511</v>
       </c>
       <c r="C281" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D281" s="1" t="s">
         <v>1074</v>
-      </c>
-      <c r="D281" s="1" t="s">
-        <v>1075</v>
       </c>
       <c r="E281" s="1" t="s">
         <v>13</v>
@@ -13280,7 +13299,7 @@
         <v>37</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H281" s="1" t="s">
         <v>205</v>
@@ -13289,7 +13308,7 @@
         <v>908</v>
       </c>
       <c r="J281" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K281" s="6"/>
     </row>
@@ -13301,10 +13320,10 @@
         <v>90732448</v>
       </c>
       <c r="C282" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D282" s="1" t="s">
         <v>1077</v>
-      </c>
-      <c r="D282" s="1" t="s">
-        <v>1078</v>
       </c>
       <c r="E282" s="1" t="s">
         <v>13</v>
@@ -13318,10 +13337,10 @@
       </c>
       <c r="I282" s="1"/>
       <c r="J282" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K282" s="6" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="283" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -13332,10 +13351,10 @@
         <v>90719678</v>
       </c>
       <c r="C283" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D283" s="1" t="s">
         <v>1080</v>
-      </c>
-      <c r="D283" s="1" t="s">
-        <v>1081</v>
       </c>
       <c r="E283" s="1" t="s">
         <v>13</v>
@@ -13353,10 +13372,10 @@
         <v>220</v>
       </c>
       <c r="J283" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K283" s="6" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="284" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -13367,10 +13386,10 @@
         <v>90731699</v>
       </c>
       <c r="C284" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D284" s="1" t="s">
         <v>1083</v>
-      </c>
-      <c r="D284" s="1" t="s">
-        <v>1084</v>
       </c>
       <c r="E284" s="1" t="s">
         <v>13</v>
@@ -13382,7 +13401,7 @@
       <c r="H284" s="1"/>
       <c r="I284" s="1"/>
       <c r="J284" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K284" s="6"/>
     </row>
@@ -13394,10 +13413,10 @@
         <v>90720239</v>
       </c>
       <c r="C285" s="7" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D285" s="7" t="s">
         <v>1085</v>
-      </c>
-      <c r="D285" s="7" t="s">
-        <v>1086</v>
       </c>
       <c r="E285" s="7" t="s">
         <v>13</v>
@@ -13415,10 +13434,10 @@
         <v>82</v>
       </c>
       <c r="J285" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K285" s="8" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
   </sheetData>
